--- a/Case4_Value_at_Risk.xlsx
+++ b/Case4_Value_at_Risk.xlsx
@@ -142,6 +142,49 @@
     <definedName function="false" hidden="false" name="pooling_gain_250" vbProcedure="false">Assumptions!$C$57</definedName>
     <definedName function="false" hidden="false" name="price_band_pct" vbProcedure="false">Assumptions!$C$132</definedName>
     <definedName function="false" hidden="false" name="process_leak_pct" vbProcedure="false">Assumptions!$C$74</definedName>
+    <definedName function="false" hidden="false" name="rd_advert_auc_age" vbProcedure="false">Assumptions!$C$181</definedName>
+    <definedName function="false" hidden="false" name="rd_advert_auc_all" vbProcedure="false">Assumptions!$C$183</definedName>
+    <definedName function="false" hidden="false" name="rd_advert_auc_mileage" vbProcedure="false">Assumptions!$C$182</definedName>
+    <definedName function="false" hidden="false" name="rd_engine_auc" vbProcedure="false">Assumptions!$C$178</definedName>
+    <definedName function="false" hidden="false" name="rd_event_24m" vbProcedure="false">Assumptions!$C$157</definedName>
+    <definedName function="false" hidden="false" name="rd_event_36m" vbProcedure="false">Assumptions!$C$156</definedName>
+    <definedName function="false" hidden="false" name="rd_event_60m" vbProcedure="false">Assumptions!$C$158</definedName>
+    <definedName function="false" hidden="false" name="rd_event_artefact_36m" vbProcedure="false">Assumptions!$C$159</definedName>
+    <definedName function="false" hidden="false" name="rd_market_median_age" vbProcedure="false">Assumptions!$C$162</definedName>
+    <definedName function="false" hidden="false" name="rd_market_median_km" vbProcedure="false">Assumptions!$C$161</definedName>
+    <definedName function="false" hidden="false" name="rd_market_share_old" vbProcedure="false">Assumptions!$C$160</definedName>
+    <definedName function="false" hidden="false" name="rd_mileage_exit_elasticity" vbProcedure="false">Assumptions!$C$170</definedName>
+    <definedName function="false" hidden="false" name="rd_mileage_market_elasticity" vbProcedure="false">Assumptions!$C$171</definedName>
+    <definedName function="false" hidden="false" name="rd_model_auc" vbProcedure="false">Assumptions!$C$176</definedName>
+    <definedName function="false" hidden="false" name="rd_model_auc_young" vbProcedure="false">Assumptions!$C$180</definedName>
+    <definedName function="false" hidden="false" name="rd_model_lift10" vbProcedure="false">Assumptions!$C$177</definedName>
+    <definedName function="false" hidden="false" name="rd_model_net_auc" vbProcedure="false">Assumptions!$C$179</definedName>
+    <definedName function="false" hidden="false" name="rd_model_within_age_auc" vbProcedure="false">Assumptions!$C$185</definedName>
+    <definedName function="false" hidden="false" name="rd_model_within_age_engine" vbProcedure="false">Assumptions!$C$186</definedName>
+    <definedName function="false" hidden="false" name="rd_mot_id_chance" vbProcedure="false">Assumptions!$C$174</definedName>
+    <definedName function="false" hidden="false" name="rd_mot_id_cross_release" vbProcedure="false">Assumptions!$C$172</definedName>
+    <definedName function="false" hidden="false" name="rd_mot_id_make_model" vbProcedure="false">Assumptions!$C$173</definedName>
+    <definedName function="false" hidden="false" name="rd_mot_odometer_monotone" vbProcedure="false">Assumptions!$C$175</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_bovag_gap" vbProcedure="false">Assumptions!$C$154</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_group_make_hi" vbProcedure="false">Assumptions!$C$191</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_group_make_lo" vbProcedure="false">Assumptions!$C$190</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_keeper_changes" vbProcedure="false">Assumptions!$C$153</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_make15_spread" vbProcedure="false">Assumptions!$C$192</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_make_hi" vbProcedure="false">Assumptions!$C$189</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_make_lo" vbProcedure="false">Assumptions!$C$188</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_make_spread" vbProcedure="false">Assumptions!$C$187</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_market_value" vbProcedure="false">Assumptions!$C$166</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_market_value_group" vbProcedure="false">Assumptions!$C$167</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_parc_measured" vbProcedure="false">Assumptions!$C$151</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_peak_age" vbProcedure="false">Assumptions!$C$148</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_peak_rate" vbProcedure="false">Assumptions!$C$147</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_peak_vs_trough" vbProcedure="false">Assumptions!$C$150</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_stellantis_share" vbProcedure="false">Assumptions!$C$152</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_transfer_rate" vbProcedure="false">Assumptions!$C$146</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_trough_rate" vbProcedure="false">Assumptions!$C$149</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_used_sales_2025" vbProcedure="false">Assumptions!$C$155</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_value_advert_priced" vbProcedure="false">Assumptions!$C$169</definedName>
+    <definedName function="false" hidden="false" name="rd_nl_wave_value" vbProcedure="false">Assumptions!$C$168</definedName>
     <definedName function="false" hidden="false" name="recoverable_share" vbProcedure="false">Assumptions!$C$75</definedName>
     <definedName function="false" hidden="false" name="retained_1y_pooled" vbProcedure="false">Assumptions!$C$52</definedName>
     <definedName function="false" hidden="false" name="retained_1y_uk" vbProcedure="false">Assumptions!$C$33</definedName>
@@ -159,6 +202,10 @@
     <definedName function="false" hidden="false" name="tesla_pre_announcement" vbProcedure="false">Assumptions!$C$71</definedName>
     <definedName function="false" hidden="false" name="thin_share_of_book" vbProcedure="false">Assumptions!$C$77</definedName>
     <definedName function="false" hidden="false" name="upgrade_capture_uplift" vbProcedure="false">Assumptions!$C$79</definedName>
+    <definedName function="false" hidden="false" name="up_ct_top_decile" vbProcedure="false">Assumptions!$C$163</definedName>
+    <definedName function="false" hidden="false" name="up_gap_vs_response" vbProcedure="false">Assumptions!$C$184</definedName>
+    <definedName function="false" hidden="false" name="up_random_top_decile" vbProcedure="false">Assumptions!$C$165</definedName>
+    <definedName function="false" hidden="false" name="up_response_top_decile" vbProcedure="false">Assumptions!$C$164</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -170,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="954">
   <si>
     <t xml:space="preserve">Case 4 - value at risk</t>
   </si>
@@ -190,10 +237,10 @@
     <t xml:space="preserve">The four tiers</t>
   </si>
   <si>
-    <t xml:space="preserve">MEASURED (80 inputs) - our own analysis of 3.9 million used-car listings from 29 sources. The source column names the report and `check_assumptions.py` re-reads the figure out of it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOURCED (23 inputs) - published figures with a URL: Stellantis's FY2025 results and Form 20-F, Eurostat and ONS price indices, one academic paper.</t>
+    <t xml:space="preserve">MEASURED (126 inputs) - our own analysis of 3.9 million used-car listings from 29 sources. The source column names the report and `check_assumptions.py` re-reads the figure out of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOURCED (24 inputs) - published figures with a URL: Stellantis's FY2025 results and Form 20-F, Eurostat and ONS price indices, one academic paper.</t>
   </si>
   <si>
     <t xml:space="preserve">ASSUMPTION (22 inputs) - our judgement, each with a low and a high and a caveat saying what it rests on. These are the rows a pilot should replace with evidence.</t>
@@ -1888,6 +1935,513 @@
     <t xml:space="preserve">UK auction (trade) prices from Glass's CAP, 1999-2004, 2,320 model-months, 47-48 models, 70.22% of UK registrations. A conference paper; no journal version found, and the paper never names the source of its discount variable. Model fixed effects, year and month effects and macro controls, but not a causal design - a model that needs discounting may be a weak model anyway, though age-of-design and new-model dummies absorb the main lifecycle channel. Table 5 coefficient -0.0015 per percentage point, t 2.48. This is the substitution channel - today's discounts against today's used cars - and is the smaller of the two.</t>
   </si>
   <si>
+    <t xml:space="preserve">rd_nl_transfer_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch cars that change keeper in a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of the fleet a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_base_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. Read the level as good to about ten per cent - see rd_nl_bovag_gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_peak_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keeper-change rate at the age it peaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. The peak sits at the same age in the previous twelve months too, so it is an age effect and not the 2021 registration cohort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_peak_age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age at which cars come to market fastest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. Whole years of age, from the year of first admission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_trough_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keeper-change rate at the quietest age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. The quietest age is nine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_peak_vs_trough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak keeper-change rate against the quietest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. This is the whole of layer 1's claim: age alone nearly doubles the chance a car comes to market.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_parc_measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cars behind the Dutch base hazard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. Ages one to twenty-five only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_stellantis_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group brands as a share of the Dutch fleet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW's open vehicle register, twelve months to September 2026, passenger cars first put on Dutch plates when new. A keeper change is not a sale to a new customer: it counts a car going into dealer stock and a car moving inside a family. The level is Dutch and the Netherlands taxes and leases cars unusually; the project has measured three times that a shape travels between markets and a level does not. Brands matched with build_unified.STELLANTIS across the 16 spellings RDW uses. The group's own curve tracks the fleet's, so the shape is not a brand-mix artefact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_keeper_changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch keeper changes counted in twelve months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keeper changes a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every passenger car, imports included, and including cars since exported or scrapped, because a car sold in November and exported in March was still a sale. This is the count held against BOVAG's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_bovag_gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Dutch count against BOVAG's published one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low in the direction the method predicts: a snapshot shows only the current keeper, so a car that changed hands twice inside the year counts once. Treat the Dutch level as good to about ten per cent and never quote it as exact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_used_sales_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used cars sold in the Netherlands, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOVAG and RDC, 'Recordjaar 2025: verkoop gebruikte auto's stijgt naar 2,1 miljoen'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bovag.nl/pers/persberichten/recordjaar-2025-verkoop-gebruikte-auto-s-stijgt-naar-2-1-miljoen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The motor trade's own count, from RDC's registrations, not ours. Used as the outside check on the Dutch base hazard. Calendar 2025; our window is September 2025 to September 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_event_36m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excess adverts at 36 months, the three-year contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% over trend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_events_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three European advert sources that record a registration month (de_2023, eu_2025_11, pt_standvirtual), 202,906 adverts. Excess over a smooth age trend with source and registration-calendar-month effects absorbed, so each contract length is measured against the other whole-year ages. Adverts are not returns: a lease car that goes straight to auction never appears. Negative in all twelve specifications tried and in two of three sources. This is layer 3's negative result: no contract-end spike exists in public data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_event_24m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excess adverts at 24 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three European advert sources that record a registration month (de_2023, eu_2025_11, pt_standvirtual), 202,906 adverts. Excess over a smooth age trend with source and registration-calendar-month effects absorbed, so each contract length is measured against the other whole-year ages. Adverts are not returns: a lease car that goes straight to auction never appears. Range crosses zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_event_60m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excess adverts at 60 months, before robustness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three European advert sources that record a registration month (de_2023, eu_2025_11, pt_standvirtual), 202,906 adverts. Excess over a smooth age trend with source and registration-calendar-month effects absorbed, so each contract length is measured against the other whole-year ages. Adverts are not returns: a lease car that goes straight to auction never appears. DO NOT QUOTE THIS AS A FINDING. It is produced entirely by eu_2025_11 (+94.6%); the other two sources read +7.5% and -1.4%, and across twelve specifications it swings from +7.1% to +30.7%. It is the lumpy registration-year composition of one day's scrape. Registered so the number has its refutation attached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_event_artefact_36m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-year artefact at 36 months if the trap is missed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources that record only a registration year put every car on a whole number of years, so the same test reads a huge spike at every contract length. This is the artefact, measured, and the reason any age-at-listing analysis must filter to month-precision sources first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_market_share_old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of cars on sale aged 15+, per 10% stronger market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percentage points per 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_market_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia, 52 monthly ss.com snapshots 2019-2023, 936,494 rows, over a window in which the index rises 71%. Linear trend and calendar-month effects removed. TWO READINGS, not separable here: a stronger market may pull older cars onto the market, or older cars may simply sell slower and pile up on display. lv_ss has no advert id, so this is the stock on sale, not the flow onto sale. Never present it as proof of the first reading. Our quality-adjusted index; Eurostat's official index gives +0.066, same sign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_market_median_km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median mileage on sale, per 10% stronger market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">km per 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia, 52 monthly ss.com snapshots 2019-2023, 936,494 rows, over a window in which the index rises 71%. Linear trend and calendar-month effects removed. TWO READINGS, not separable here: a stronger market may pull older cars onto the market, or older cars may simply sell slower and pile up on display. lv_ss has no advert id, so this is the stock on sale, not the flow onto sale. Never present it as proof of the first reading. Our index; Eurostat's gives +9,980 km, same sign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_market_median_age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median age on sale, per 10% stronger market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">years per 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia, 52 monthly ss.com snapshots 2019-2023, 936,494 rows, over a window in which the index rises 71%. Linear trend and calendar-month effects removed. TWO READINGS, not separable here: a stronger market may pull older cars onto the market, or older cars may simply sell slower and pile up on display. lv_ss has no advert id, so this is the stock on sale, not the flow onto sale. Never present it as proof of the first reading. Our index; Eurostat's gives +0.709 years, same sign. All eight measures across the two indices agree in sign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">up_ct_top_decile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplift in the top decile, class-transformation model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/uplift_engine_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MineThatData / Hillstrom 2008 e-mail trial, 64,000 customers, treatment randomised by the publisher, 32,103 held out. A 2008 CLOTHING RETAILER, not cars: no coefficient here transfers to an automotive book. Outcome is a website visit, not a purchase. Quoted only alongside up_response_top_decile: the uplift model does NOT beat the plain response model here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">up_response_top_decile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplift in the top decile, ordinary response model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MineThatData / Hillstrom 2008 e-mail trial, 64,000 customers, treatment randomised by the publisher, 32,103 held out. A 2008 CLOTHING RETAILER, not cars: no coefficient here transfers to an automotive book. Outcome is a website visit, not a purchase. This is the baseline uplift modelling is meant to beat and does not beat here. The difference against the best uplift model is -0.14 points, range -3.36 to +2.88, which contains zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">up_random_top_decile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplift in a random tenth, no model at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MineThatData / Hillstrom 2008 e-mail trial, 64,000 customers, treatment randomised by the publisher, 32,103 held out. A 2008 CLOTHING RETAILER, not cars: no coefficient here transfers to an automotive book. Outcome is a website visit, not a purchase. The floor. Modelling at all clearly beats this; which model is used does not separate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_market_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of Dutch cars changing keeper in a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR billion a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_value_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW register (cars and keeper-change rate, measured) times RDW's official catalogue price for the vintages still on the road times the measured Dutch value-retained curve. Dutch only; the project has measured three times that a shape travels and a level does not. Retention is measured on advert prices, so it inherits the advert-is-not-a-sale caveat. NOT the value-at-risk model: that prices what the group loses when a residual is wrong and its headline is unchanged at EUR 913m/EUR 1,460m. Do not add the two. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_market_value_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...of which the group's own brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW register (cars and keeper-change rate, measured) times RDW's official catalogue price for the vintages still on the road times the measured Dutch value-retained curve. Dutch only; the project has measured three times that a shape travels and a level does not. Retention is measured on advert prices, so it inherits the advert-is-not-a-sale caveat. NOT the value-at-risk model: that prices what the group loses when a residual is wrong and its headline is unchanged at EUR 913m/EUR 1,460m. Do not add the two. Cars and rate measured for the group's brands specifically; the price curve is the market's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_wave_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value in the replacement wave, ages four to six</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW register (cars and keeper-change rate, measured) times RDW's official catalogue price for the vintages still on the road times the measured Dutch value-retained curve. Dutch only; the project has measured three times that a shape travels and a level does not. Retention is measured on advert prices, so it inherits the advert-is-not-a-sale caveat. NOT the value-at-risk model: that prices what the group loses when a residual is wrong and its headline is unchanged at EUR 913m/EUR 1,460m. Do not add the two. 30% of the total on 226,347 cars: where a high hazard meets a car still worth something.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_value_advert_priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What pricing the same cars from our adverts would say</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO NOT QUOTE AS A VALUE. Registered as the size of the error: our Dutch adverts are one premium dealer scrape whose median asking price is not monotone in age, and pricing the flow from them overstates it 2.4x against official catalogue prices. It is the measured reason the level comes from the register, not the listings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_mileage_exit_elasticity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet-exit hazard per doubling of cohort mileage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_mileage_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK DVSA anonymised MOT extracts, Open Government Licence v3.0, streamed not stored. Whole years of age on both sides (test or advert year minus year of first use). An MOT starts at three, so no car younger than that is seen. British: layer 1 is Dutch, and this layer is a shape, which the project has measured three times is the half that travels. Elasticity 0.626, standard error 0.026. Monotone across all ten deciles, 0.61x at the least-driven tenth to 1.78x at the most-driven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_mileage_market_elasticity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coming-to-market hazard per doubling of cohort mileage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK DVSA anonymised MOT extracts, Open Government Licence v3.0, streamed not stored. Whole years of age on both sides (test or advert year minus year of first use). An MOT starts at three, so no car younger than that is seen. British: layer 1 is Dutch, and this layer is a shape, which the project has measured three times is the half that travels. Elasticity 0.041, standard error 0.024 - no effect. And a single slope is the wrong summary: the profile is arched, both ends under-represented (0.85x least-driven, 0.84x most-driven) and the middle at 1.05x. THIS IS THE EVENT THE LEDGER CARES ABOUT, so layer 2 contributes almost nothing to a to-market hazard. Quote it with rd_mileage_exit_elasticity, never alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_mot_id_cross_release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle id identical across two releases of test year 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share of shared tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_mot_id_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK DVSA anonymised MOT extracts, Open Government Licence v3.0. DVSA's user guide states the id is derived from the registration and the VIN; this is the measurement rather than the claim. It is what makes layer 2 possible at all. 202,060 tests present in both the May 2025 and the June 2026 release, built thirteen months apart by pipelines that format the odometer differently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_mot_id_make_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make and model agree when a car is followed a year on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share of followed cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK DVSA anonymised MOT extracts, Open Government Licence v3.0. DVSA's user guide states the id is derived from the registration and the VIN; this is the measurement rather than the claim. It is what makes layer 2 possible at all. 249,716 January 2024 cars found again in January or February 2025. Quote it with rd_mot_id_chance or it means nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_mot_id_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make and model agreeing by chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The null for rd_mot_id_make_model, from the sample's own make and model distribution. First-use date by chance is 0.0007. Ids are also sparse - a 303k sample spans 3,707 to 1,499,987,839 - so a coincidental collision is itself rare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_mot_odometer_monotone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Followed cars whose odometer has not gone backwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK DVSA anonymised MOT extracts, Open Government Licence v3.0. DVSA's user guide states the id is derived from the registration and the VIN; this is the measurement rather than the claim. It is what makes layer 2 possible at all. The 0.71% that fall are mis-keyed or rolled-back readings, which is why DfT's own note on MOT odometers cleans pairs before annualising. Not evidence against the id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_model_auc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learned readiness model, AUC on held-out cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_model_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK MOT panel: 759,541 cars tested March 2024, followed to July 2025, 8.67% never tested again. A quarter sample by a mixing hash of the vehicle id (sampling the raw id gives old, worn-out cars). 30% held out on a fixed seed. PREDICTS A CAR LEAVING THE FLEET, NOT A CUSTOMER REPLACING IT: the MOT register has no keeper, no contract and no price. Well calibrated: predicted and actual agree within 0.3 points across all ten risk deciles. Now includes a tier of prior-year test history (the public stand-in for a service record), which took it from 0.712 to 0.723.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_model_lift10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learned model, leavers in the top tenth against average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK MOT panel: 759,541 cars tested March 2024, followed to July 2025, 8.67% never tested again. A quarter sample by a mixing hash of the vehicle id (sampling the raw id gives old, worn-out cars). 30% held out on a fixed seed. PREDICTS A CAR LEAVING THE FLEET, NOT A CUSTOMER REPLACING IT: the MOT register has no keeper, no contract and no price. Against 2.86x for the two-layer engine: about 12% more leavers for the same number of calls. Was 3.20x before the history tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_engine_auc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The two-layer engine's AUC on the same cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK MOT panel: 759,541 cars tested March 2024, followed to July 2025, 8.67% never tested again. A quarter sample by a mixing hash of the vehicle id (sampling the raw id gives old, worn-out cars). 30% held out on a fixed seed. PREDICTS A CAR LEAVING THE FLEET, NOT A CUSTOMER REPLACING IT: the MOT register has no keeper, no contract and no price. Age alone gives 0.664. Most of the gain is age and mileage; every other public field is worth a further +0.018. Quote with rd_model_auc or it overstates what a modelling programme buys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_model_net_auc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A neural network on the same fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK MOT panel: 759,541 cars tested March 2024, followed to July 2025, 8.67% never tested again. A quarter sample by a mixing hash of the vehicle id (sampling the raw id gives old, worn-out cars). 30% held out on a fixed seed. PREDICTS A CAR LEAVING THE FLEET, NOT A CUSTOMER REPLACING IT: the MOT register has no keeper, no contract and no price. Boosted trees beat it (0.712). Included because it is the first thing anyone asks; on a table of ten columns trees are the right tool and this is the measurement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_model_auc_young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learned model on cars aged three to six</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK MOT panel: 759,541 cars tested March 2024, followed to July 2025, 8.67% never tested again. A quarter sample by a mixing hash of the vehicle id (sampling the raw id gives old, worn-out cars). 30% held out on a fixed seed. PREDICTS A CAR LEAVING THE FLEET, NOT A CUSTOMER REPLACING IT: the MOT register has no keeper, no contract and no price. The weakest slice, and the one a lease book is made of. Public data can see why an old car dies; it cannot see why a young one changes hands, because that is a contract date and an equity position. The engine is weakest exactly where the group's own data would be strongest. Was 0.604 before the history tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_advert_auc_age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telling an advert from a car on the road, age only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis/readiness_advert_model_report.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A classifier trained to tell 354,112 UK adverts of October 2022 from 3,095,658 MOT tests of the September-November parc - the density-ratio estimator done with a model. Both sides rounded to the nearest thousand miles first, because 30.9% of advert mileages are exact multiples of a thousand against 0.11% of MOT readings and the model would otherwise identify the file from the digits. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_advert_auc_mileage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...adding the odometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A classifier trained to tell 354,112 UK adverts of October 2022 from 3,095,658 MOT tests of the September-November parc - the density-ratio estimator done with a model. Both sides rounded to the nearest thousand miles first, because 30.9% of advert mileages are exact multiples of a thousand against 0.11% of MOT readings and the model would otherwise identify the file from the digits. Mileage is worth +0.009 over age. Confirms the 0.041 elasticity in readiness_mileage_report.md by a second method free to find any shape: mileage does not predict coming to market.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_advert_auc_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...adding make and fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A classifier trained to tell 354,112 UK adverts of October 2022 from 3,095,658 MOT tests of the September-November parc - the density-ratio estimator done with a model. Both sides rounded to the nearest thousand miles first, because 30.9% of advert mileages are exact multiples of a thousand against 0.11% of MOT readings and the model would otherwise identify the file from the digits. DO NOT READ THE +0.051 AS A REPLACEMENT SIGNAL. A density ratio over makes is only that if the adverts fairly sample the cars coming to market; they are one site's stock and its brand mix is not the fleet's. Where the outcome IS observed per car (rd_model_auc) make is worth +0.002, against +0.082 here - the gap is about the files.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">up_gap_vs_response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best uplift model against the ordinary response model, top decile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MineThatData / Hillstrom 2008 e-mail trial, 64,000 customers, randomised by the publisher, 32,103 held out, 400-draw bootstrap. The range contains zero: uplift modelling does not beat a plain response model here. A 2008 clothing retailer and a website visit, not cars and not a purchase - no coefficient transfers. Quoted in section 7.4 of the solution document as the reason to measure before assuming.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_model_within_age_auc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learned model, ranking cars of the SAME age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The measure that matters for a call list, which is built from cars of similar age. Age alone scores 0.500 here by construction; mileage takes it to 0.618, what the car is to 0.643, and a year of history to 0.667. Global AUC understates what the extra fields buy because age already separates most pairs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_model_within_age_engine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The two-layer engine, ranking cars of the same age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote with rd_model_within_age_auc: within an age band the learned model is worth +0.049 over the engine, against +0.029 on global AUC. The extra fields matter more than a headline AUC suggests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_make_spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread in keeper-change rate across makes at the peak age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW register, 12 months to Sept 2026, cars first registered in NL when new, makes with at least 3,000 cars of the 2021 registration year - so every car compared is exactly five years old. A keeper change is not a sale to a new customer. This is the answer to 'so only age matters': at one age the makes differ by 60%. It is why the engine needs a layer beyond the age curve. Across all 24 makes with 3,000+ cars of that year; the deck figure shows the fifteen largest, where the spread is 1.60x (rd_nl_make15_spread).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_make_lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest make at the peak age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW register, 12 months to Sept 2026, cars first registered in NL when new, makes with at least 3,000 cars of the 2021 registration year - so every car compared is exactly five years old. A keeper change is not a sale to a new customer. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_make_hi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest make at the peak age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_group_make_lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group brands, lowest at the peak age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDW register, 12 months to Sept 2026, cars first registered in NL when new, makes with at least 3,000 cars of the 2021 registration year - so every car compared is exactly five years old. A keeper change is not a sale to a new customer. The group's own four brands differ from each other by 43% at one age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_group_make_hi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group brands, highest at the peak age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd_nl_make15_spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread across the fifteen largest makes at the peak age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The figure in Case4_Deck_Figure_AI_Alt_SameAge quotes this one, because fifteen rows is what the block has room for. Across all 24 qualifying makes it is 1.75x (rd_nl_make_spread). Same register, same age, same twelve months.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value at risk - summary</t>
   </si>
   <si>
@@ -1930,9 +2484,6 @@
     <t xml:space="preserve">How much of this is evidence?</t>
   </si>
   <si>
-    <t xml:space="preserve">share</t>
-  </si>
-  <si>
     <t xml:space="preserve">meaning</t>
   </si>
   <si>
@@ -2020,9 +2571,6 @@
     <t xml:space="preserve">Measured value curve (share of list price)</t>
   </si>
   <si>
-    <t xml:space="preserve">years</t>
-  </si>
-  <si>
     <t xml:space="preserve">retained</t>
   </si>
   <si>
@@ -2504,6 +3052,9 @@
   </si>
   <si>
     <t xml:space="preserve">Stellantis FY2025 results press release (SEC-filed), results by segment  https://www.sec.gov/Archives/edgar/data/1605484/000160548426000019/stellantisnvfy2025pressrel.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOVAG and RDC, 'Recordjaar 2025: verkoop gebruikte auto's stijgt naar 2,1 miljoen'  https://www.bovag.nl/pers/persberichten/recordjaar-2025-verkoop-gebruikte-auto-s-stijgt-naar-2-1-miljoen</t>
   </si>
   <si>
     <t xml:space="preserve">Stellantis Form 20-F FY2025: "Third party estimates are utilized in conjunction with proprietary modelling"  https://www.sec.gov/Archives/edgar/data/1605484/000160548426000021/stellantis-20251231.htm</t>
@@ -3226,7 +3777,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L192"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -8050,6 +8601,1540 @@
       </c>
       <c r="L145" s="5" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K146" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="L146" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K147" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="L147" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K148" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="L148" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D149" s="5"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K149" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="L149" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C150" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K150" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="L150" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>6759930</v>
+      </c>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K151" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="L151" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K152" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="L152" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>1931085</v>
+      </c>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H153" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K153" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="L153" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K154" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="L154" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>2124429</v>
+      </c>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="I155" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="J155" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="K155" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="L155" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="C156" s="5" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="D156" s="5" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K156" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="L156" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="I157" s="5"/>
+      <c r="J157" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K157" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="L157" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="C158" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D158" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="I158" s="5"/>
+      <c r="J158" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K158" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="L158" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>716</v>
+      </c>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="I159" s="5"/>
+      <c r="J159" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K159" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="L159" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="I160" s="5"/>
+      <c r="J160" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="L160" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>5686</v>
+      </c>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="I161" s="5"/>
+      <c r="J161" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K161" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="L161" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="D162" s="5"/>
+      <c r="E162" s="5"/>
+      <c r="F162" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="I162" s="5"/>
+      <c r="J162" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K162" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="L162" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>8.64</v>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="I163" s="5"/>
+      <c r="J163" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="L163" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="I164" s="5"/>
+      <c r="J164" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K164" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="L164" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H165" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="I165" s="5"/>
+      <c r="J165" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K165" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="L165" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="C166" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="I166" s="5"/>
+      <c r="J166" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K166" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="L166" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="I167" s="5"/>
+      <c r="J167" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K167" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="L167" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H168" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="I168" s="5"/>
+      <c r="J168" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K168" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="L168" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="C169" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H169" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="I169" s="5"/>
+      <c r="J169" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K169" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="L169" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H170" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="I170" s="5"/>
+      <c r="J170" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K170" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="L170" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H171" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="I171" s="5"/>
+      <c r="J171" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K171" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="L171" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="C172" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="I172" s="5"/>
+      <c r="J172" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K172" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="L172" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="C173" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H173" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="I173" s="5"/>
+      <c r="J173" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K173" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="L173" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>0.0088</v>
+      </c>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="I174" s="5"/>
+      <c r="J174" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K174" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="L174" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>0.9929</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="I175" s="5"/>
+      <c r="J175" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K175" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="L175" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I176" s="5"/>
+      <c r="J176" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K176" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="L176" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="C177" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D177" s="5"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I177" s="5"/>
+      <c r="J177" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K177" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="L177" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="D178" s="5"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I178" s="5"/>
+      <c r="J178" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K178" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="L178" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="D179" s="5"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I179" s="5"/>
+      <c r="J179" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K179" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="L179" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="D180" s="5"/>
+      <c r="E180" s="5"/>
+      <c r="F180" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I180" s="5"/>
+      <c r="J180" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="L180" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="D181" s="5"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="I181" s="5"/>
+      <c r="J181" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K181" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="L181" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="D182" s="5"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="I182" s="5"/>
+      <c r="J182" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K182" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="L182" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="D183" s="5"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="I183" s="5"/>
+      <c r="J183" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K183" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="L183" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="E184" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="I184" s="5"/>
+      <c r="J184" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K184" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="L184" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D185" s="5"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I185" s="5"/>
+      <c r="J185" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K185" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="L185" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="D186" s="5"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="I186" s="5"/>
+      <c r="J186" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K186" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="L186" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D187" s="5"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I187" s="5"/>
+      <c r="J187" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K187" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="L187" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I188" s="5"/>
+      <c r="J188" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K188" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="L188" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I189" s="5"/>
+      <c r="J189" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K189" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="L189" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D190" s="5"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I190" s="5"/>
+      <c r="J190" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K190" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="L190" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I191" s="5"/>
+      <c r="J191" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K191" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="L191" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="I192" s="5"/>
+      <c r="J192" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="K192" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="L192" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -8078,12 +10163,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>572</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>573</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8092,18 +10177,18 @@
         <v>28</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>574</v>
+        <v>743</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>575</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>576</v>
+        <v>745</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">eu_revenue_eur_m * Assumptions!$D$73/100 * (Assumptions!$D$74/100 + Assumptions!$D$76/100)</f>
@@ -8118,12 +10203,12 @@
         <v>1733.19</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>577</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>578</v>
+        <v>747</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">eu_shipments * Assumptions!$D$78/100 * Assumptions!$D$79/100 * Assumptions!$D$80 / 1000000</f>
@@ -8138,12 +10223,12 @@
         <v>261.45</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>579</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>580</v>
+        <v>749</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - Assumptions!$D$77/100) + curve_1y_p80_unknown/2/retained_1y_pooled * Assumptions!$D$77/100))</f>
@@ -8158,12 +10243,12 @@
         <v>316.322444933921</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>581</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>582</v>
+        <v>751</v>
       </c>
       <c r="B8" s="13" t="n">
         <f aca="false">eu_revenue_eur_m * Assumptions!$D$73/100 * (Assumptions!$D$74/100 + Assumptions!$D$76/100) + eu_shipments * Assumptions!$D$78/100 * Assumptions!$D$79/100 * Assumptions!$D$80 / 1000000 + buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - Assumptions!$D$77/100) + curve_1y_p80_unknown/2/retained_1y_pooled * Assumptions!$D$77/100))</f>
@@ -8180,19 +10265,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>583</v>
+        <v>752</v>
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100) + eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000 + buyback_payables_current_eur_m * (ABS(level_1y_worst)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100))</f>
         <v>1459.94943105727</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>584</v>
+        <v>753</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>585</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8201,15 +10286,15 @@
         <v>48</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>586</v>
+        <v>684</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>587</v>
+        <v>755</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>588</v>
+        <v>756</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100))</f>
@@ -8220,12 +10305,12 @@
         <v>0.326861204721511</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>589</v>
+        <v>757</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>590</v>
+        <v>758</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000</f>
@@ -8236,12 +10321,12 @@
         <v>0.0654753117380011</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>591</v>
+        <v>759</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>592</v>
+        <v>760</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100)</f>
@@ -8252,34 +10337,34 @@
         <v>0.607663483540488</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>593</v>
+        <v>761</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>594</v>
+        <v>762</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>595</v>
+        <v>763</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>596</v>
+        <v>764</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>597</v>
+        <v>765</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>598</v>
+        <v>766</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>599</v>
+        <v>767</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8424,7 +10509,7 @@
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>600</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -8453,34 +10538,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>601</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>602</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>603</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>604</v>
+        <v>772</v>
       </c>
       <c r="B6" s="19" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100</f>
         <v>4621.84</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>605</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>606</v>
+        <v>774</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * process_leak_pct/100</f>
@@ -8492,7 +10577,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>607</v>
+        <v>775</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * targeting_leak_pct/100</f>
@@ -8504,7 +10589,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>608</v>
+        <v>776</v>
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100)</f>
@@ -8513,24 +10598,24 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>609</v>
+        <v>777</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * process_leak_pct/100 * recoverable_share/100</f>
         <v>27.73104</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>610</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>611</v>
+        <v>779</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>612</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -8558,22 +10643,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>613</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>614</v>
+        <v>782</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>615</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>0</v>
@@ -8596,7 +10681,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>617</v>
+        <v>784</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>100</v>
@@ -8622,17 +10707,17 @@
         <v>52</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>618</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>619</v>
+        <v>786</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>620</v>
+        <v>787</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">loan_deposit_pct</f>
@@ -8641,7 +10726,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>621</v>
+        <v>788</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">loan_term_months</f>
@@ -8650,7 +10735,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>622</v>
+        <v>789</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">loan_apr</f>
@@ -8659,45 +10744,45 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>623</v>
+        <v>790</v>
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">100 - loan_deposit_pct</f>
         <v>85</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>624</v>
+        <v>791</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>625</v>
+        <v>792</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>626</v>
+        <v>793</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>627</v>
+        <v>794</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>628</v>
+        <v>795</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>629</v>
+        <v>796</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>630</v>
+        <v>797</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>631</v>
+        <v>798</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>632</v>
+        <v>799</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>633</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10715,7 +12800,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>634</v>
+        <v>801</v>
       </c>
       <c r="B80" s="0" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX($D$30:$D$78&gt;=loan_deposit_pct,0),0)+11,"not within the term")</f>
@@ -10732,40 +12817,40 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="11" t="s">
-        <v>635</v>
+        <v>802</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>636</v>
+        <v>803</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>637</v>
+        <v>804</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="17" t="s">
-        <v>638</v>
+        <v>805</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>639</v>
+        <v>806</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="18" t="s">
-        <v>640</v>
+        <v>807</v>
       </c>
       <c r="B86" s="21" t="n">
         <f aca="false">eu_shipments * finance_penetration/100</f>
         <v>996000</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>641</v>
+        <v>808</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="18" t="s">
-        <v>642</v>
+        <v>809</v>
       </c>
       <c r="B87" s="21" t="n">
         <f aca="false">eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100</f>
@@ -10777,14 +12862,14 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>643</v>
+        <v>810</v>
       </c>
       <c r="B88" s="13" t="n">
         <f aca="false">eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000</f>
         <v>59.76</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>644</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -10813,46 +12898,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>645</v>
+        <v>812</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>646</v>
+        <v>813</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>647</v>
+        <v>814</v>
       </c>
       <c r="B5" s="19" t="n">
         <f aca="false">buyback_payables_eur_m</f>
         <v>7889</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>648</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>649</v>
+        <v>816</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">buyback_payables_current_eur_m</f>
         <v>5313</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>650</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>651</v>
+        <v>818</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>652</v>
+        <v>819</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * ABS(level_1y_p10_core)/100</f>
@@ -10861,7 +12946,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>653</v>
+        <v>820</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * ABS(level_1y_p10)/100</f>
@@ -10870,7 +12955,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>654</v>
+        <v>821</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * ABS(level_1y_worst)/100</f>
@@ -10879,48 +12964,48 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>655</v>
+        <v>822</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>656</v>
+        <v>823</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100)</f>
         <v>21.9424559471366</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>657</v>
+        <v>824</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>658</v>
+        <v>825</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100</f>
         <v>37.3021751101322</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>659</v>
+        <v>826</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>660</v>
+        <v>827</v>
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100))</f>
         <v>298.329631057269</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>661</v>
+        <v>828</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>662</v>
+        <v>829</v>
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * (ABS(level_1y_worst)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100))</f>
@@ -10929,12 +13014,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>663</v>
+        <v>830</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>664</v>
+        <v>831</v>
       </c>
       <c r="B20" s="19" t="n">
         <f aca="false">buyback_value_decrease_2023_eur_m</f>
@@ -10943,7 +13028,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>665</v>
+        <v>832</v>
       </c>
       <c r="B21" s="19" t="n">
         <f aca="false">buyback_value_decrease_2024_eur_m</f>
@@ -10952,41 +13037,41 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>666</v>
+        <v>833</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">buyback_value_decrease_2025_eur_m</f>
         <v>358</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>667</v>
+        <v>834</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>668</v>
+        <v>835</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>669</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>670</v>
+        <v>837</v>
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">buyback_payables_eur_m * (ABS(level_3y_p10_core)/100 + (curve_p80_known/2/retained_3y_pooled * (1 - thin_share_of_book/100) + curve_p80_unknown/2/retained_3y_pooled * thin_share_of_book/100))</f>
         <v>867.79</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>671</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>672</v>
+        <v>839</v>
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">buyback_payables_eur_m * (ABS(level_3y_worst)/100 + (curve_p80_known/2/retained_3y_pooled * (1 - thin_share_of_book/100) + curve_p80_unknown/2/retained_3y_pooled * thin_share_of_book/100))</f>
@@ -10995,36 +13080,36 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>673</v>
+        <v>840</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>674</v>
+        <v>841</v>
       </c>
       <c r="B30" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m * curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100 * pooling_gain_100/100</f>
         <v>1.60399352973568</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>675</v>
+        <v>842</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>676</v>
+        <v>843</v>
       </c>
       <c r="B31" s="19" t="n">
         <f aca="false">buyback_payables_eur_m * (ABS(level_3m_p5)-ABS(level_1m_p5))/100</f>
         <v>134.113</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>677</v>
+        <v>844</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>678</v>
+        <v>845</v>
       </c>
     </row>
   </sheetData>
@@ -11053,82 +13138,82 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>679</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>680</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>681</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>682</v>
+        <v>849</v>
       </c>
       <c r="B6" s="19" t="n">
         <f aca="false">new_car_price_eur</f>
         <v>11969</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>683</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>684</v>
+        <v>851</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">new_car_price_eur * pl_sale_margin_pct_list/100</f>
         <v>1196.9</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>685</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>686</v>
+        <v>853</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">-new_car_price_eur * pl_incentive_pct_list/100</f>
         <v>-957.52</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>687</v>
+        <v>854</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>688</v>
+        <v>855</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">pl_finance_income_eur</f>
         <v>450</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>689</v>
+        <v>856</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>690</v>
+        <v>857</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">pl_credit_loss_eur</f>
         <v>-66</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>691</v>
+        <v>858</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>692</v>
+        <v>859</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">pl_service_parts_eur</f>
@@ -11137,27 +13222,27 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>693</v>
+        <v>860</v>
       </c>
       <c r="B12" s="19" t="n">
         <f aca="false">-new_car_price_eur * pl_warranty_pct_list/100</f>
         <v>-299.225</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>694</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>695</v>
+        <v>862</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>696</v>
+        <v>863</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>697</v>
+        <v>864</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">pl_recon_logistics_eur</f>
@@ -11166,7 +13251,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>698</v>
+        <v>865</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">pl_remarketing_margin_eur</f>
@@ -11175,7 +13260,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>699</v>
+        <v>866</v>
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">SUM(B7:B15)</f>
@@ -11184,31 +13269,31 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>700</v>
+        <v>867</v>
       </c>
       <c r="B18" s="19" t="n">
         <f aca="false">-new_car_price_eur * retained_4y_uk/100 * ABS(level_3y_p10_core)/100</f>
         <v>-543.75167</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>701</v>
+        <v>868</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>702</v>
+        <v>869</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">-new_car_price_eur * curve_p80_known/100</f>
         <v>-287.256</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>703</v>
+        <v>870</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>704</v>
+        <v>871</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">B16 + SUM(B18:B19)</f>
@@ -11217,12 +13302,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>705</v>
+        <v>872</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>706</v>
+        <v>873</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">eu_revenue_eur_m*1000000/eu_shipments</f>
@@ -11231,7 +13316,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>707</v>
+        <v>874</v>
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">eu_aoi_2024_eur_m*1000000/eu_shipments_2024</f>
@@ -11240,7 +13325,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>708</v>
+        <v>875</v>
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">eu_aoi_eur_m*1000000/eu_shipments</f>
@@ -11249,19 +13334,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>709</v>
+        <v>876</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">B26-B27</f>
         <v>1200.49857816359</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>710</v>
+        <v>877</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>711</v>
+        <v>878</v>
       </c>
       <c r="B30" s="19" t="n">
         <f aca="false">(eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100))*1000000/eu_shipments</f>
@@ -11270,7 +13355,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>712</v>
+        <v>879</v>
       </c>
       <c r="B31" s="19" t="n">
         <f aca="false">(eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000)*1000000/eu_shipments</f>
@@ -11279,7 +13364,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>713</v>
+        <v>880</v>
       </c>
       <c r="B32" s="19" t="n">
         <f aca="false">(buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100)))*1000000/eu_shipments</f>
@@ -11288,7 +13373,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>714</v>
+        <v>881</v>
       </c>
       <c r="B33" s="13" t="n">
         <f aca="false">(eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100) + eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000 + buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100)))*1000000/eu_shipments</f>
@@ -11297,7 +13382,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>715</v>
+        <v>882</v>
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">(eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100) + eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000 + buyback_payables_current_eur_m * (ABS(level_1y_worst)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100)))*1000000/eu_shipments</f>
@@ -11306,36 +13391,36 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>716</v>
+        <v>883</v>
       </c>
       <c r="B35" s="22" t="n">
         <f aca="false">-B33/B27</f>
         <v>1.40201295093282</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>717</v>
+        <v>884</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>718</v>
+        <v>885</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>719</v>
+        <v>886</v>
       </c>
       <c r="B40" s="19" t="n">
         <f aca="false">inv_people_eur_m + inv_platform_eur_m + inv_change_eur_m</f>
         <v>20</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>720</v>
+        <v>887</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>721</v>
+        <v>888</v>
       </c>
       <c r="B41" s="19" t="n">
         <f aca="false">eu_revenue_eur_m * incentive_pct_revenue/100 * (process_leak_pct/100 + targeting_leak_pct/100) + eu_shipments * finance_penetration/100 * upgrade_capture_uplift/100 * margin_per_repeat_sale / 1000000 + buyback_payables_current_eur_m * (ABS(level_1y_p10_core)/100 + (curve_1y_p80_known/2/retained_1y_pooled * (1 - thin_share_of_book/100) + curve_1y_p80_unknown/2/retained_1y_pooled * thin_share_of_book/100))</f>
@@ -11344,7 +13429,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>722</v>
+        <v>889</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">B40/B41</f>
@@ -11353,23 +13438,23 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>723</v>
+        <v>890</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
-        <v>724</v>
+        <v>891</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>725</v>
+        <v>892</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>726</v>
+        <v>893</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>727</v>
+        <v>894</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11463,75 +13548,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>728</v>
+        <v>895</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>729</v>
+        <v>896</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>730</v>
+        <v>897</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>731</v>
+        <v>898</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">dpt_passthrough</f>
         <v>0.3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>732</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>733</v>
+        <v>900</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">hk_passthrough_36m</f>
         <v>6.5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>734</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>735</v>
+        <v>902</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">hk_passthrough_now</f>
         <v>1.5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>736</v>
+        <v>903</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>737</v>
+        <v>904</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">pl_incentive_pct_list</f>
         <v>8</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>738</v>
+        <v>905</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>739</v>
+        <v>906</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>740</v>
+        <v>907</v>
       </c>
       <c r="B12" s="19" t="n">
         <f aca="false">new_car_price_eur</f>
@@ -11540,7 +13625,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>741</v>
+        <v>908</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">new_car_price_eur * pl_incentive_pct_list/100</f>
@@ -11549,19 +13634,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>742</v>
+        <v>909</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">new_car_price_eur * retained_4y_uk/100</f>
         <v>7061.71</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>743</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>744</v>
+        <v>911</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">1-(1-pl_incentive_pct_list/100)^dpt_passthrough</f>
@@ -11570,7 +13655,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>745</v>
+        <v>912</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">(hk_passthrough_36m + hk_passthrough_now)/100 * pl_incentive_pct_list/10</f>
@@ -11579,7 +13664,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>746</v>
+        <v>913</v>
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">B14 * B15</f>
@@ -11588,7 +13673,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>747</v>
+        <v>914</v>
       </c>
       <c r="B18" s="19" t="n">
         <f aca="false">B14 * B16</f>
@@ -11597,19 +13682,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>748</v>
+        <v>915</v>
       </c>
       <c r="B20" s="23" t="n">
         <f aca="false">B17 / B13</f>
         <v>0.182193570671545</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>749</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>750</v>
+        <v>917</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B18 / B13</f>
@@ -11618,24 +13703,24 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>751</v>
+        <v>918</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>752</v>
+        <v>919</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">buyback_payables_current_eur_m</f>
         <v>5313</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>753</v>
+        <v>920</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>754</v>
+        <v>921</v>
       </c>
       <c r="B26" s="13" t="n">
         <f aca="false">B25 * B15</f>
@@ -11644,7 +13729,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>755</v>
+        <v>922</v>
       </c>
       <c r="B27" s="13" t="n">
         <f aca="false">B25 * B16</f>
@@ -11653,32 +13738,32 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>756</v>
+        <v>923</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>757</v>
+        <v>924</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>758</v>
+        <v>925</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>759</v>
+        <v>926</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>760</v>
+        <v>927</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>761</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>
@@ -11697,7 +13782,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -11709,12 +13794,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>762</v>
+        <v>929</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>763</v>
+        <v>930</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11722,7 +13807,7 @@
         <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>596</v>
+        <v>764</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>27</v>
@@ -11751,7 +13836,7 @@
         <v>40</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>764</v>
+        <v>931</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>120</v>
@@ -11771,7 +13856,7 @@
         <v>40</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>49</v>
@@ -11791,7 +13876,7 @@
         <v>40</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>44</v>
@@ -11809,7 +13894,7 @@
         <v>40</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>766</v>
+        <v>933</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>107</v>
@@ -12189,7 +14274,7 @@
         <v>40</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>767</v>
+        <v>934</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>69</v>
@@ -12209,7 +14294,7 @@
         <v>40</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>768</v>
+        <v>935</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>64</v>
@@ -12229,7 +14314,7 @@
         <v>40</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>768</v>
+        <v>935</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>420</v>
@@ -12609,7 +14694,7 @@
         <v>40</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>769</v>
+        <v>936</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>568</v>
@@ -12629,7 +14714,7 @@
         <v>40</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>769</v>
+        <v>936</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>571</v>
@@ -12647,7 +14732,7 @@
         <v>40</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>770</v>
+        <v>937</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>103</v>
@@ -12907,7 +14992,7 @@
         <v>40</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>771</v>
+        <v>938</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>114</v>
@@ -13007,7 +15092,7 @@
         <v>40</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>772</v>
+        <v>939</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>95</v>
@@ -13087,7 +15172,7 @@
         <v>40</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>773</v>
+        <v>940</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>90</v>
@@ -13105,7 +15190,7 @@
         <v>40</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>774</v>
+        <v>941</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>74</v>
@@ -13125,7 +15210,7 @@
         <v>40</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>775</v>
+        <v>942</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>83</v>
@@ -13145,7 +15230,7 @@
         <v>40</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>775</v>
+        <v>942</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>83</v>
@@ -13165,7 +15250,7 @@
         <v>40</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>776</v>
+        <v>943</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>78</v>
@@ -13605,7 +15690,7 @@
         <v>40</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>777</v>
+        <v>944</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>414</v>
@@ -13625,7 +15710,7 @@
         <v>40</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>53</v>
@@ -13645,7 +15730,7 @@
         <v>40</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>777</v>
+        <v>944</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>417</v>
@@ -13705,7 +15790,7 @@
         <v>40</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="F103" s="6"/>
     </row>
@@ -13723,7 +15808,7 @@
         <v>40</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="F104" s="6"/>
     </row>
@@ -13867,741 +15952,1681 @@
         <v>261</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>169</v>
+        <v>707</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>62</v>
+        <v>0.662</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>163</v>
+        <v>708</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>166</v>
+        <v>714</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>90</v>
+        <v>0.722</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>163</v>
+        <v>708</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>172</v>
+        <v>711</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>68</v>
+        <v>0.671</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>163</v>
+        <v>708</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C115" s="5"/>
-      <c r="D115" s="7" t="s">
-        <v>40</v>
+        <v>698</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>778</v>
+        <v>692</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>253</v>
+        <v>620</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>2.7</v>
+        <v>-9.1</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>254</v>
+        <v>617</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>296</v>
+        <v>615</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>68</v>
+        <v>-16.9</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>297</v>
+        <v>617</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>499</v>
+        <v>623</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>472</v>
+        <v>20</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>473</v>
+        <v>617</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>502</v>
+        <v>626</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>472</v>
+        <v>716</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>473</v>
+        <v>617</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>477</v>
+        <v>638</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>472</v>
+        <v>0.449</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>473</v>
+        <v>631</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>480</v>
+        <v>634</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>472</v>
+        <v>5686</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>473</v>
+        <v>631</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>483</v>
+        <v>629</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>472</v>
+        <v>0.039</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>473</v>
+        <v>631</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>486</v>
+        <v>666</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>472</v>
+        <v>1.54</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>473</v>
+        <v>668</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>496</v>
+        <v>671</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>472</v>
+        <v>1.03</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>473</v>
+        <v>668</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>472</v>
+        <v>0.723</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>473</v>
+        <v>692</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>493</v>
+        <v>704</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>472</v>
+        <v>0.615</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>473</v>
+        <v>692</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>470</v>
+        <v>695</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>472</v>
+        <v>3.34</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>473</v>
+        <v>692</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>467</v>
+        <v>701</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>305</v>
+        <v>0.703</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>460</v>
+        <v>692</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>459</v>
+        <v>720</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>305</v>
+        <v>0.667</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>460</v>
+        <v>692</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>464</v>
+        <v>723</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>305</v>
+        <v>0.618</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>460</v>
+        <v>692</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>526</v>
+        <v>683</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>472</v>
+        <v>0.0088</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>473</v>
+        <v>676</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>529</v>
+        <v>674</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>472</v>
+        <v>0.9999</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>473</v>
+        <v>676</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>532</v>
+        <v>679</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>472</v>
+        <v>1</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>473</v>
+        <v>676</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>535</v>
+        <v>687</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>472</v>
+        <v>0.9929</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>473</v>
+        <v>676</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
-        <v>509</v>
+        <v>54</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>506</v>
+        <v>606</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>472</v>
+        <v>-9.1</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>473</v>
+        <v>575</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>508</v>
+        <v>607</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>509</v>
+        <v>54</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>511</v>
+        <v>737</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>472</v>
+        <v>32.7</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>473</v>
+        <v>575</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>509</v>
+        <v>54</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>518</v>
+        <v>734</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D137" s="10" t="s">
-        <v>472</v>
+        <v>22.8</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>473</v>
+        <v>575</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="s">
-        <v>509</v>
+        <v>54</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>515</v>
+        <v>602</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>472</v>
+        <v>1931085</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>473</v>
+        <v>575</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>516</v>
+        <v>604</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>405</v>
+        <v>739</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>11969</v>
+        <v>1.6</v>
       </c>
       <c r="D139" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>268</v>
+        <v>575</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>441</v>
+        <v>732</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>-66</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>305</v>
+        <v>34.8</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>779</v>
+        <v>575</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>436</v>
+        <v>729</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="D141" s="9" t="s">
-        <v>305</v>
+        <v>19.8</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>780</v>
+        <v>575</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>427</v>
+        <v>726</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>305</v>
+        <v>1.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>428</v>
+        <v>575</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>450</v>
+        <v>652</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>-500</v>
-      </c>
-      <c r="D143" s="9" t="s">
-        <v>305</v>
+        <v>13</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>781</v>
+        <v>654</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>455</v>
+        <v>657</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>305</v>
+        <v>2.4</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>782</v>
+        <v>654</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>457</v>
+        <v>658</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>422</v>
+        <v>594</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D145" s="9" t="s">
-        <v>305</v>
+        <v>6759930</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>783</v>
+        <v>575</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>425</v>
+        <v>596</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="s">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="D146" s="9" t="s">
-        <v>305</v>
+        <v>5</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>784</v>
+        <v>575</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>448</v>
+        <v>585</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C150" s="5" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>2124429</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C158" s="5"/>
+      <c r="D158" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>8.64</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="C166" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C169" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C172" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C173" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C177" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B186" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>11969</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>-66</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-500</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C193" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B194" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="C147" s="5" t="n">
+      <c r="C194" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="D147" s="9" t="s">
+      <c r="D194" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="E147" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="F147" s="6" t="s">
+      <c r="E194" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="F194" s="6" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="5" t="s">
+    <row r="195" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B195" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="C148" s="5" t="n">
+      <c r="C195" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D148" s="10" t="s">
+      <c r="D195" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="E148" s="6" t="s">
+      <c r="E195" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="F195" s="6" t="s">
         <v>523</v>
       </c>
     </row>
